--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/42.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/42.xlsx
@@ -426,13 +426,13 @@
         <v>-14.73252777330457</v>
       </c>
       <c r="E2">
-        <v>-5.247340150992919</v>
+        <v>-7.554980652984752</v>
       </c>
       <c r="F2">
-        <v>1.648700322911751</v>
+        <v>2.506322348908524</v>
       </c>
       <c r="G2">
-        <v>-17.66846932916001</v>
+        <v>-19.13899341143359</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.35315323749605</v>
       </c>
       <c r="E3">
-        <v>-6.517757656722072</v>
+        <v>-6.662227112656232</v>
       </c>
       <c r="F3">
-        <v>1.715915710709708</v>
+        <v>2.453565285759029</v>
       </c>
       <c r="G3">
-        <v>-17.04904406747247</v>
+        <v>-18.73319558934464</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.77932901270031</v>
       </c>
       <c r="E4">
-        <v>-7.490929827933246</v>
+        <v>-8.769853110455648</v>
       </c>
       <c r="F4">
-        <v>2.010522920780547</v>
+        <v>2.197135872548414</v>
       </c>
       <c r="G4">
-        <v>-16.54635563943197</v>
+        <v>-18.54407781996742</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.03432311903982</v>
       </c>
       <c r="E5">
-        <v>-8.224752430494551</v>
+        <v>-8.22722774444415</v>
       </c>
       <c r="F5">
-        <v>2.129951962711763</v>
+        <v>2.526239614741435</v>
       </c>
       <c r="G5">
-        <v>-15.94756570299259</v>
+        <v>-17.87141817069479</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.12908901081756</v>
       </c>
       <c r="E6">
-        <v>-9.860951564024004</v>
+        <v>-9.049256249122163</v>
       </c>
       <c r="F6">
-        <v>2.292048552826376</v>
+        <v>2.821782879977437</v>
       </c>
       <c r="G6">
-        <v>-14.8824014904028</v>
+        <v>-16.8791433363443</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.09080745155076</v>
       </c>
       <c r="E7">
-        <v>-10.66520432423175</v>
+        <v>-9.422937284862286</v>
       </c>
       <c r="F7">
-        <v>2.594046456864992</v>
+        <v>2.530394705633878</v>
       </c>
       <c r="G7">
-        <v>-14.85849359680969</v>
+        <v>-16.6483469876284</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.956010269087107</v>
       </c>
       <c r="E8">
-        <v>-10.73065893471105</v>
+        <v>-10.77685095106579</v>
       </c>
       <c r="F8">
-        <v>2.026734070853333</v>
+        <v>3.034661705353271</v>
       </c>
       <c r="G8">
-        <v>-14.11816605847999</v>
+        <v>-16.22103989353941</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.75157403746471</v>
       </c>
       <c r="E9">
-        <v>-10.69379087778055</v>
+        <v>-10.63466160814896</v>
       </c>
       <c r="F9">
-        <v>2.625110234469973</v>
+        <v>3.173911922498673</v>
       </c>
       <c r="G9">
-        <v>-14.59162459007838</v>
+        <v>-14.92783236240506</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.516794024114044</v>
       </c>
       <c r="E10">
-        <v>-10.93851885509607</v>
+        <v>-11.74339459700254</v>
       </c>
       <c r="F10">
-        <v>3.064302347760243</v>
+        <v>3.281750447729919</v>
       </c>
       <c r="G10">
-        <v>-12.71984342324594</v>
+        <v>-14.74667018448312</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.263554543655034</v>
       </c>
       <c r="E11">
-        <v>-11.74413802182968</v>
+        <v>-12.11380705543002</v>
       </c>
       <c r="F11">
-        <v>3.251887802858997</v>
+        <v>3.414458219128011</v>
       </c>
       <c r="G11">
-        <v>-12.5986396056035</v>
+        <v>-13.76995277715107</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.020113809944648</v>
       </c>
       <c r="E12">
-        <v>-13.0020543614711</v>
+        <v>-12.86524758043125</v>
       </c>
       <c r="F12">
-        <v>3.326966054044327</v>
+        <v>3.708841770000094</v>
       </c>
       <c r="G12">
-        <v>-11.54662310277456</v>
+        <v>-13.08854060663673</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.785082275503592</v>
       </c>
       <c r="E13">
-        <v>-12.92910735776181</v>
+        <v>-13.41501231671013</v>
       </c>
       <c r="F13">
-        <v>3.507629671125288</v>
+        <v>3.670206714333525</v>
       </c>
       <c r="G13">
-        <v>-11.65287779688828</v>
+        <v>-12.51954579284343</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.582401619809374</v>
       </c>
       <c r="E14">
-        <v>-14.58782104988316</v>
+        <v>-14.1127310532247</v>
       </c>
       <c r="F14">
-        <v>3.418223977341138</v>
+        <v>4.103013771683016</v>
       </c>
       <c r="G14">
-        <v>-10.03543145200521</v>
+        <v>-11.72771609596484</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.414869674009082</v>
       </c>
       <c r="E15">
-        <v>-14.92551450949365</v>
+        <v>-14.97372913976358</v>
       </c>
       <c r="F15">
-        <v>3.599508869974198</v>
+        <v>4.138267431611357</v>
       </c>
       <c r="G15">
-        <v>-9.912334844534216</v>
+        <v>-11.57947018584765</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.3017562743422748</v>
       </c>
       <c r="E16">
-        <v>-16.45172414750767</v>
+        <v>-16.10907175357534</v>
       </c>
       <c r="F16">
-        <v>3.656876626087675</v>
+        <v>4.488651932382298</v>
       </c>
       <c r="G16">
-        <v>-9.245751703297399</v>
+        <v>-10.48322375352837</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.7484375267192694</v>
       </c>
       <c r="E17">
-        <v>-16.46599042840845</v>
+        <v>-17.43652531042836</v>
       </c>
       <c r="F17">
-        <v>4.672355657831533</v>
+        <v>4.621101253150716</v>
       </c>
       <c r="G17">
-        <v>-8.920110919703248</v>
+        <v>-9.640389244945492</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.724452099370694</v>
       </c>
       <c r="E18">
-        <v>-17.79762211585425</v>
+        <v>-17.53099010201159</v>
       </c>
       <c r="F18">
-        <v>4.221725447443408</v>
+        <v>4.522863506117917</v>
       </c>
       <c r="G18">
-        <v>-8.188688631173836</v>
+        <v>-9.225689436486988</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.616352745789807</v>
       </c>
       <c r="E19">
-        <v>-19.55168108035969</v>
+        <v>-18.2469165169742</v>
       </c>
       <c r="F19">
-        <v>4.703621557082798</v>
+        <v>4.867361628124565</v>
       </c>
       <c r="G19">
-        <v>-7.564212884074789</v>
+        <v>-8.817893742099685</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.422079212652823</v>
       </c>
       <c r="E20">
-        <v>-17.38712286171952</v>
+        <v>-19.34652074733581</v>
       </c>
       <c r="F20">
-        <v>4.530728026240096</v>
+        <v>5.1927410304746</v>
       </c>
       <c r="G20">
-        <v>-8.149395619705286</v>
+        <v>-8.250154696454711</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.131824340116392</v>
       </c>
       <c r="E21">
-        <v>-19.79748889261966</v>
+        <v>-19.7688234280557</v>
       </c>
       <c r="F21">
-        <v>4.787280037826325</v>
+        <v>4.968558303520163</v>
       </c>
       <c r="G21">
-        <v>-7.697826876131081</v>
+        <v>-7.445779066443526</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.750482325732225</v>
       </c>
       <c r="E22">
-        <v>-19.17926262086231</v>
+        <v>-20.11627693427953</v>
       </c>
       <c r="F22">
-        <v>4.885350454643759</v>
+        <v>4.692422029796949</v>
       </c>
       <c r="G22">
-        <v>-7.645888723235473</v>
+        <v>-7.648850612974091</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.270141496192177</v>
       </c>
       <c r="E23">
-        <v>-21.14486125098657</v>
+        <v>-19.73860881566757</v>
       </c>
       <c r="F23">
-        <v>5.173163395276836</v>
+        <v>4.601167419969749</v>
       </c>
       <c r="G23">
-        <v>-7.256661949752462</v>
+        <v>-6.837308489060299</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.699502223353273</v>
       </c>
       <c r="E24">
-        <v>-20.99933272616457</v>
+        <v>-20.66115334082908</v>
       </c>
       <c r="F24">
-        <v>5.139120808491387</v>
+        <v>4.671487528793399</v>
       </c>
       <c r="G24">
-        <v>-6.53350658397081</v>
+        <v>-6.986321958087272</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.036745813430994</v>
       </c>
       <c r="E25">
-        <v>-21.30797031934656</v>
+        <v>-20.72341828501091</v>
       </c>
       <c r="F25">
-        <v>4.904720997990823</v>
+        <v>4.547620094317983</v>
       </c>
       <c r="G25">
-        <v>-5.990090540308945</v>
+        <v>-6.659203493054551</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.295357307126592</v>
       </c>
       <c r="E26">
-        <v>-19.38380412539879</v>
+        <v>-21.82199251896396</v>
       </c>
       <c r="F26">
-        <v>4.762023115714968</v>
+        <v>4.176405466836247</v>
       </c>
       <c r="G26">
-        <v>-6.216541304652929</v>
+        <v>-6.01885311346924</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.482642975427099</v>
       </c>
       <c r="E27">
-        <v>-20.78205332249485</v>
+        <v>-21.82315541813491</v>
       </c>
       <c r="F27">
-        <v>4.674375217559558</v>
+        <v>4.156524649169058</v>
       </c>
       <c r="G27">
-        <v>-6.222133519567094</v>
+        <v>-6.189439165052582</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.613636630472175</v>
       </c>
       <c r="E28">
-        <v>-19.93641796464651</v>
+        <v>-21.37419327392095</v>
       </c>
       <c r="F28">
-        <v>4.589658083275252</v>
+        <v>4.104039290527681</v>
       </c>
       <c r="G28">
-        <v>-6.227258411199449</v>
+        <v>-5.854660775389534</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.699337844691692</v>
       </c>
       <c r="E29">
-        <v>-21.30954023322734</v>
+        <v>-21.05371487525188</v>
       </c>
       <c r="F29">
-        <v>4.955726892450799</v>
+        <v>3.906513426595334</v>
       </c>
       <c r="G29">
-        <v>-6.877148451520688</v>
+        <v>-6.000060973902406</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.750509734892162</v>
       </c>
       <c r="E30">
-        <v>-21.71049956094894</v>
+        <v>-21.70860154337349</v>
       </c>
       <c r="F30">
-        <v>5.087952554020462</v>
+        <v>3.985900845010027</v>
       </c>
       <c r="G30">
-        <v>-6.390108826559322</v>
+        <v>-6.004363480988561</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.775102992033904</v>
       </c>
       <c r="E31">
-        <v>-20.01387950906588</v>
+        <v>-21.83884209730879</v>
       </c>
       <c r="F31">
-        <v>4.479942477509264</v>
+        <v>4.081540831867647</v>
       </c>
       <c r="G31">
-        <v>-6.204427449750163</v>
+        <v>-5.998473641191009</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.775678911631713</v>
       </c>
       <c r="E32">
-        <v>-20.7982716127183</v>
+        <v>-20.2640440400056</v>
       </c>
       <c r="F32">
-        <v>4.661185951772184</v>
+        <v>4.073338337845127</v>
       </c>
       <c r="G32">
-        <v>-5.463383262030204</v>
+        <v>-5.749902037926523</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.754242960172698</v>
       </c>
       <c r="E33">
-        <v>-21.04216894776886</v>
+        <v>-21.04155427249278</v>
       </c>
       <c r="F33">
-        <v>4.159311277112076</v>
+        <v>4.087901036786342</v>
       </c>
       <c r="G33">
-        <v>-7.036414314556963</v>
+        <v>-6.436191079337063</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.707917723852536</v>
       </c>
       <c r="E34">
-        <v>-19.16561932166025</v>
+        <v>-21.03947766683037</v>
       </c>
       <c r="F34">
-        <v>4.645776661345308</v>
+        <v>4.260227964325528</v>
       </c>
       <c r="G34">
-        <v>-6.575826753792757</v>
+        <v>-6.236675366939594</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.636291242224061</v>
       </c>
       <c r="E35">
-        <v>-20.17052618060444</v>
+        <v>-19.94450842030727</v>
       </c>
       <c r="F35">
-        <v>4.507775622243327</v>
+        <v>4.572111604949153</v>
       </c>
       <c r="G35">
-        <v>-6.639194746508259</v>
+        <v>-6.751036434046961</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.535899788782986</v>
       </c>
       <c r="E36">
-        <v>-18.1343063451128</v>
+        <v>-19.57146282589985</v>
       </c>
       <c r="F36">
-        <v>4.445382989464468</v>
+        <v>4.50174013734653</v>
       </c>
       <c r="G36">
-        <v>-7.085929696472017</v>
+        <v>-6.342729033719799</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>6.40718741052929</v>
       </c>
       <c r="E37">
-        <v>-18.80576432642048</v>
+        <v>-19.45400585642237</v>
       </c>
       <c r="F37">
-        <v>5.113090191225815</v>
+        <v>4.517787270673562</v>
       </c>
       <c r="G37">
-        <v>-6.388035895353979</v>
+        <v>-6.791006933736905</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>6.251757113723088</v>
       </c>
       <c r="E38">
-        <v>-18.52357853616633</v>
+        <v>-19.14130226935338</v>
       </c>
       <c r="F38">
-        <v>4.701283904272097</v>
+        <v>4.546442155871202</v>
       </c>
       <c r="G38">
-        <v>-7.076178565424209</v>
+        <v>-7.020940431365434</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>6.072292773472532</v>
       </c>
       <c r="E39">
-        <v>-19.42190153288145</v>
+        <v>-18.51109813613522</v>
       </c>
       <c r="F39">
-        <v>5.561583213714719</v>
+        <v>4.953790169463054</v>
       </c>
       <c r="G39">
-        <v>-6.229169476240144</v>
+        <v>-7.416371639369226</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.876171850385652</v>
       </c>
       <c r="E40">
-        <v>-18.09455595952287</v>
+        <v>-18.26983393706461</v>
       </c>
       <c r="F40">
-        <v>4.949196043847127</v>
+        <v>5.081835889118191</v>
       </c>
       <c r="G40">
-        <v>-7.135262326265694</v>
+        <v>-7.887637145511086</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.666370158770811</v>
       </c>
       <c r="E41">
-        <v>-16.9885350176644</v>
+        <v>-17.90760745815836</v>
       </c>
       <c r="F41">
-        <v>5.296580197885128</v>
+        <v>5.132805335412444</v>
       </c>
       <c r="G41">
-        <v>-7.608713025630315</v>
+        <v>-8.062752838960009</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.452112572242597</v>
       </c>
       <c r="E42">
-        <v>-15.82323529056666</v>
+        <v>-17.81124464899969</v>
       </c>
       <c r="F42">
-        <v>5.096415155407461</v>
+        <v>5.418447953450186</v>
       </c>
       <c r="G42">
-        <v>-7.519404674657512</v>
+        <v>-8.660041597259498</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.234525960456004</v>
       </c>
       <c r="E43">
-        <v>-16.70782361743057</v>
+        <v>-16.7130317444319</v>
       </c>
       <c r="F43">
-        <v>4.993994152990525</v>
+        <v>5.454251649333986</v>
       </c>
       <c r="G43">
-        <v>-8.025949172459084</v>
+        <v>-8.547998882387279</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.019667788500019</v>
       </c>
       <c r="E44">
-        <v>-14.60882799276415</v>
+        <v>-16.6318696887221</v>
       </c>
       <c r="F44">
-        <v>5.256270183330098</v>
+        <v>5.325811626795117</v>
       </c>
       <c r="G44">
-        <v>-7.924303747920976</v>
+        <v>-9.078859855310482</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.805839008870244</v>
       </c>
       <c r="E45">
-        <v>-13.70676710585669</v>
+        <v>-16.46348604197958</v>
       </c>
       <c r="F45">
-        <v>5.07060654060584</v>
+        <v>5.31208557893073</v>
       </c>
       <c r="G45">
-        <v>-7.578509321455726</v>
+        <v>-8.905031258944977</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.59358271791193</v>
       </c>
       <c r="E46">
-        <v>-14.88741294879967</v>
+        <v>-15.15307726440365</v>
       </c>
       <c r="F46">
-        <v>4.932057122283206</v>
+        <v>5.490502663615298</v>
       </c>
       <c r="G46">
-        <v>-7.757552880141979</v>
+        <v>-9.545769334102069</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.379327551175872</v>
       </c>
       <c r="E47">
-        <v>-12.89330667614179</v>
+        <v>-14.40987671067088</v>
       </c>
       <c r="F47">
-        <v>4.958614581216958</v>
+        <v>5.893801617342265</v>
       </c>
       <c r="G47">
-        <v>-8.42004237385993</v>
+        <v>-9.397612189300981</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.160284159681421</v>
       </c>
       <c r="E48">
-        <v>-11.79590780099367</v>
+        <v>-14.64657237728419</v>
       </c>
       <c r="F48">
-        <v>5.109243253007214</v>
+        <v>5.719758312544478</v>
       </c>
       <c r="G48">
-        <v>-8.764233803146238</v>
+        <v>-9.956633958756226</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.933485956190777</v>
       </c>
       <c r="E49">
-        <v>-13.90939813318375</v>
+        <v>-13.48296716040698</v>
       </c>
       <c r="F49">
-        <v>4.620509798825117</v>
+        <v>5.808534447102502</v>
       </c>
       <c r="G49">
-        <v>-8.37350193540645</v>
+        <v>-9.719912525190802</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.695921667967498</v>
       </c>
       <c r="E50">
-        <v>-11.96417100460778</v>
+        <v>-13.66928852686143</v>
       </c>
       <c r="F50">
-        <v>5.464641033299897</v>
+        <v>5.875839298579961</v>
       </c>
       <c r="G50">
-        <v>-8.628519467066395</v>
+        <v>-9.977619123779595</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.448207428095562</v>
       </c>
       <c r="E51">
-        <v>-12.33316306476217</v>
+        <v>-13.12986528678138</v>
       </c>
       <c r="F51">
-        <v>4.816127104261415</v>
+        <v>5.553978800957019</v>
       </c>
       <c r="G51">
-        <v>-8.551924136880018</v>
+        <v>-9.727106431911615</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.189090321751239</v>
       </c>
       <c r="E52">
-        <v>-12.43715532312455</v>
+        <v>-12.63876050725438</v>
       </c>
       <c r="F52">
-        <v>4.592781028383807</v>
+        <v>5.999691822442126</v>
       </c>
       <c r="G52">
-        <v>-8.161127000525454</v>
+        <v>-10.45292214643161</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.922558781353986</v>
       </c>
       <c r="E53">
-        <v>-10.70262475826846</v>
+        <v>-11.99443960874313</v>
       </c>
       <c r="F53">
-        <v>5.067838136745684</v>
+        <v>5.435340021528074</v>
       </c>
       <c r="G53">
-        <v>-9.165321189306676</v>
+        <v>-10.92913109745674</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.647232973417171</v>
       </c>
       <c r="E54">
-        <v>-10.03934029684804</v>
+        <v>-12.30397429557127</v>
       </c>
       <c r="F54">
-        <v>4.982289321588968</v>
+        <v>5.962310915023396</v>
       </c>
       <c r="G54">
-        <v>-9.450872684331987</v>
+        <v>-10.28610209392095</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.369067985200191</v>
       </c>
       <c r="E55">
-        <v>-10.38307667893615</v>
+        <v>-11.79059584370922</v>
       </c>
       <c r="F55">
-        <v>4.692231505294305</v>
+        <v>5.793106932592763</v>
       </c>
       <c r="G55">
-        <v>-9.373984950751405</v>
+        <v>-10.84585095574482</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.087138899680122</v>
       </c>
       <c r="E56">
-        <v>-10.06202513710425</v>
+        <v>-11.59510003343821</v>
       </c>
       <c r="F56">
-        <v>4.521238249273624</v>
+        <v>5.436062357903315</v>
       </c>
       <c r="G56">
-        <v>-8.733560164945247</v>
+        <v>-10.82983403767834</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.808152225247041</v>
       </c>
       <c r="E57">
-        <v>-10.04344782284829</v>
+        <v>-11.22928517994731</v>
       </c>
       <c r="F57">
-        <v>4.888322636885003</v>
+        <v>5.595317647826326</v>
       </c>
       <c r="G57">
-        <v>-8.730730117808481</v>
+        <v>-10.99232155954005</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.531883023298662</v>
       </c>
       <c r="E58">
-        <v>-10.10666800563484</v>
+        <v>-10.78908631162874</v>
       </c>
       <c r="F58">
-        <v>5.035175610053299</v>
+        <v>5.470452858997939</v>
       </c>
       <c r="G58">
-        <v>-10.58161488493365</v>
+        <v>-11.5826004686124</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.262168413111147</v>
       </c>
       <c r="E59">
-        <v>-9.017787366913938</v>
+        <v>-10.6501572396019</v>
       </c>
       <c r="F59">
-        <v>4.477140938952996</v>
+        <v>5.780242386827287</v>
       </c>
       <c r="G59">
-        <v>-9.539662802503456</v>
+        <v>-11.55419817820568</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.9981385811244243</v>
       </c>
       <c r="E60">
-        <v>-8.623165839674028</v>
+        <v>-10.42229960668783</v>
       </c>
       <c r="F60">
-        <v>4.721267439497232</v>
+        <v>5.566217100965979</v>
       </c>
       <c r="G60">
-        <v>-10.01799559425346</v>
+        <v>-11.09391476918634</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.739829109035834</v>
       </c>
       <c r="E61">
-        <v>-8.829742417759675</v>
+        <v>-10.25507470590493</v>
       </c>
       <c r="F61">
-        <v>4.489846438177135</v>
+        <v>5.875294232828919</v>
       </c>
       <c r="G61">
-        <v>-10.0857000337348</v>
+        <v>-12.16549880272567</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.4862503672199841</v>
       </c>
       <c r="E62">
-        <v>-9.117937904800852</v>
+        <v>-10.1820031058559</v>
       </c>
       <c r="F62">
-        <v>4.322469834237078</v>
+        <v>5.576873219235591</v>
       </c>
       <c r="G62">
-        <v>-10.02543752171043</v>
+        <v>-11.99121332605672</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.2349775852904687</v>
       </c>
       <c r="E63">
-        <v>-8.212886705739516</v>
+        <v>-9.784615539873656</v>
       </c>
       <c r="F63">
-        <v>4.586823410022872</v>
+        <v>6.106604232917042</v>
       </c>
       <c r="G63">
-        <v>-10.75337055009381</v>
+        <v>-12.14369386390069</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.01346171122135381</v>
       </c>
       <c r="E64">
-        <v>-7.697535478498167</v>
+        <v>-9.855515010399804</v>
       </c>
       <c r="F64">
-        <v>4.756994925579975</v>
+        <v>5.664900509661484</v>
       </c>
       <c r="G64">
-        <v>-10.34947400275334</v>
+        <v>-12.54036778632985</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.2617984108403622</v>
       </c>
       <c r="E65">
-        <v>-8.842899791236732</v>
+        <v>-9.440725488966526</v>
       </c>
       <c r="F65">
-        <v>4.67414493142158</v>
+        <v>5.722400804559409</v>
       </c>
       <c r="G65">
-        <v>-10.25501334732997</v>
+        <v>-12.38204440209097</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.5067672939848209</v>
       </c>
       <c r="E66">
-        <v>-9.4135385676342</v>
+        <v>-9.631806435599239</v>
       </c>
       <c r="F66">
-        <v>4.287849047004475</v>
+        <v>5.454609504051995</v>
       </c>
       <c r="G66">
-        <v>-10.57335448904737</v>
+        <v>-12.65022269723472</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.7498734110288831</v>
       </c>
       <c r="E67">
-        <v>-8.29710552498439</v>
+        <v>-9.388598533628604</v>
       </c>
       <c r="F67">
-        <v>4.724431802975927</v>
+        <v>5.663293476900052</v>
       </c>
       <c r="G67">
-        <v>-11.65395472903212</v>
+        <v>-12.29032111237139</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.9861167434137028</v>
       </c>
       <c r="E68">
-        <v>-8.571192553155125</v>
+        <v>-9.883366445544103</v>
       </c>
       <c r="F68">
-        <v>4.429933937402257</v>
+        <v>5.820590506282845</v>
       </c>
       <c r="G68">
-        <v>-11.12572538665676</v>
+        <v>-12.74104528007037</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.21618368480433</v>
       </c>
       <c r="E69">
-        <v>-7.813385155192934</v>
+        <v>-9.566206462723573</v>
       </c>
       <c r="F69">
-        <v>4.730222091121495</v>
+        <v>5.941356533202179</v>
       </c>
       <c r="G69">
-        <v>-11.64499334822312</v>
+        <v>-12.8231192577812</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.436057137868247</v>
       </c>
       <c r="E70">
-        <v>-7.664575593424328</v>
+        <v>-8.717202850490796</v>
       </c>
       <c r="F70">
-        <v>4.967872415310645</v>
+        <v>5.916154283339408</v>
       </c>
       <c r="G70">
-        <v>-10.61889240157786</v>
+        <v>-12.11809942930171</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.646846752856369</v>
       </c>
       <c r="E71">
-        <v>-8.037006512555678</v>
+        <v>-9.408143546123247</v>
       </c>
       <c r="F71">
-        <v>4.136378753932974</v>
+        <v>5.453310623964406</v>
       </c>
       <c r="G71">
-        <v>-11.35294240453823</v>
+        <v>-12.5598896290099</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.846767686468357</v>
       </c>
       <c r="E72">
-        <v>-8.784356124401949</v>
+        <v>-9.184484809858581</v>
       </c>
       <c r="F72">
-        <v>4.819636068579674</v>
+        <v>6.007115651106015</v>
       </c>
       <c r="G72">
-        <v>-10.80624465492534</v>
+        <v>-12.46286652777036</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.037092503332001</v>
       </c>
       <c r="E73">
-        <v>-9.903912381968031</v>
+        <v>-8.912652975437227</v>
       </c>
       <c r="F73">
-        <v>4.482535267480026</v>
+        <v>5.83749085803476</v>
       </c>
       <c r="G73">
-        <v>-10.32068793289172</v>
+        <v>-12.28837088616183</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.217820657119702</v>
       </c>
       <c r="E74">
-        <v>-8.30446916866331</v>
+        <v>-9.031264537663006</v>
       </c>
       <c r="F74">
-        <v>4.356611825110862</v>
+        <v>5.946780682955711</v>
       </c>
       <c r="G74">
-        <v>-10.68641931042701</v>
+        <v>-12.45064693771165</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.38898116236072</v>
       </c>
       <c r="E75">
-        <v>-8.521192042015514</v>
+        <v>-9.456628135129296</v>
       </c>
       <c r="F75">
-        <v>4.352372240743335</v>
+        <v>5.49815512168236</v>
       </c>
       <c r="G75">
-        <v>-10.66405436688724</v>
+        <v>-12.58369048207479</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.550462258202735</v>
       </c>
       <c r="E76">
-        <v>-8.391400034903297</v>
+        <v>-9.984825244998341</v>
       </c>
       <c r="F76">
-        <v>4.882694708750384</v>
+        <v>6.010894663197587</v>
       </c>
       <c r="G76">
-        <v>-11.42337376674499</v>
+        <v>-12.45641929400261</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.700010102163518</v>
       </c>
       <c r="E77">
-        <v>-9.089941107260184</v>
+        <v>-9.749562436292102</v>
       </c>
       <c r="F77">
-        <v>4.487513755570851</v>
+        <v>5.974839143623336</v>
       </c>
       <c r="G77">
-        <v>-10.7219411013337</v>
+        <v>-11.76689423467138</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.837233628062726</v>
       </c>
       <c r="E78">
-        <v>-8.755806949755078</v>
+        <v>-9.990747724347546</v>
       </c>
       <c r="F78">
-        <v>4.696481030070665</v>
+        <v>6.057076145903659</v>
       </c>
       <c r="G78">
-        <v>-10.32066835230729</v>
+        <v>-11.87333820776796</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.958592970497872</v>
       </c>
       <c r="E79">
-        <v>-9.335287913063105</v>
+        <v>-10.65764132640924</v>
       </c>
       <c r="F79">
-        <v>4.131342280123953</v>
+        <v>5.846564794565026</v>
       </c>
       <c r="G79">
-        <v>-10.48913970077183</v>
+        <v>-11.82904170429054</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.062859852150464</v>
       </c>
       <c r="E80">
-        <v>-10.86872413878232</v>
+        <v>-11.63673182375829</v>
       </c>
       <c r="F80">
-        <v>4.304714607325473</v>
+        <v>5.756107074179321</v>
       </c>
       <c r="G80">
-        <v>-9.401119724659141</v>
+        <v>-11.62271194851026</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.145341944105206</v>
       </c>
       <c r="E81">
-        <v>-9.625497707596825</v>
+        <v>-11.89919816664216</v>
       </c>
       <c r="F81">
-        <v>4.264613341355949</v>
+        <v>6.074831372815264</v>
       </c>
       <c r="G81">
-        <v>-10.2223947044086</v>
+        <v>-11.60724067606333</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.201548580795508</v>
       </c>
       <c r="E82">
-        <v>-11.36927332086199</v>
+        <v>-12.35639612891326</v>
       </c>
       <c r="F82">
-        <v>4.224563434165399</v>
+        <v>6.023371533018553</v>
       </c>
       <c r="G82">
-        <v>-9.769106785521151</v>
+        <v>-11.58679462979802</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.225718035423195</v>
       </c>
       <c r="E83">
-        <v>-13.35716223616659</v>
+        <v>-13.36321761827819</v>
       </c>
       <c r="F83">
-        <v>4.686023719977725</v>
+        <v>5.927039031012193</v>
       </c>
       <c r="G83">
-        <v>-10.07946165953433</v>
+        <v>-11.30077320074631</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.210632528968643</v>
       </c>
       <c r="E84">
-        <v>-14.05380944415936</v>
+        <v>-13.76048889434334</v>
       </c>
       <c r="F84">
-        <v>4.69314436617219</v>
+        <v>6.248911125778775</v>
       </c>
       <c r="G84">
-        <v>-9.953370528017334</v>
+        <v>-11.34718962883171</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.151097654129379</v>
       </c>
       <c r="E85">
-        <v>-14.9319976723717</v>
+        <v>-15.304619639224</v>
       </c>
       <c r="F85">
-        <v>4.9123486050358</v>
+        <v>6.083045463981424</v>
       </c>
       <c r="G85">
-        <v>-9.994731249202047</v>
+        <v>-11.01474002334394</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.040399728797711</v>
       </c>
       <c r="E86">
-        <v>-17.39277953554394</v>
+        <v>-15.23019409228307</v>
       </c>
       <c r="F86">
-        <v>4.277810890817351</v>
+        <v>6.025179030691461</v>
       </c>
       <c r="G86">
-        <v>-9.960309887140514</v>
+        <v>-11.50359672654072</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.876558532759772</v>
       </c>
       <c r="E87">
-        <v>-16.09895868399938</v>
+        <v>-16.82430873545803</v>
       </c>
       <c r="F87">
-        <v>4.849871478781855</v>
+        <v>6.020449052821476</v>
       </c>
       <c r="G87">
-        <v>-9.790138943947159</v>
+        <v>-10.83845732706279</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.657790370747898</v>
       </c>
       <c r="E88">
-        <v>-18.6987609898476</v>
+        <v>-19.18898944178506</v>
       </c>
       <c r="F88">
-        <v>4.585718367907538</v>
+        <v>6.310289836856606</v>
       </c>
       <c r="G88">
-        <v>-8.99824397845379</v>
+        <v>-11.02660716288284</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.38721031073745</v>
       </c>
       <c r="E89">
-        <v>-19.84654247157722</v>
+        <v>-19.38404085844431</v>
       </c>
       <c r="F89">
-        <v>4.378790533953416</v>
+        <v>6.153102151970984</v>
       </c>
       <c r="G89">
-        <v>-8.916254849942174</v>
+        <v>-10.31836306483334</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.070430972119678</v>
       </c>
       <c r="E90">
-        <v>-20.74737400793252</v>
+        <v>-21.08656262361995</v>
       </c>
       <c r="F90">
-        <v>4.336065000051823</v>
+        <v>6.493940546792063</v>
       </c>
       <c r="G90">
-        <v>-8.339271157700068</v>
+        <v>-10.16699078806829</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.714580825420588</v>
       </c>
       <c r="E91">
-        <v>-22.48795995490022</v>
+        <v>-22.60174963877787</v>
       </c>
       <c r="F91">
-        <v>4.990435486628098</v>
+        <v>6.422931236289283</v>
       </c>
       <c r="G91">
-        <v>-8.447400366430207</v>
+        <v>-9.816861220209498</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.329433362886145</v>
       </c>
       <c r="E92">
-        <v>-24.57416784189749</v>
+        <v>-24.7752164957098</v>
       </c>
       <c r="F92">
-        <v>4.001749170160387</v>
+        <v>6.173433601505295</v>
       </c>
       <c r="G92">
-        <v>-9.340855907262474</v>
+        <v>-9.699784989765615</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.9214343391272222</v>
       </c>
       <c r="E93">
-        <v>-26.84380646026715</v>
+        <v>-27.24681332117188</v>
       </c>
       <c r="F93">
-        <v>4.3574219684308</v>
+        <v>6.080560361773025</v>
       </c>
       <c r="G93">
-        <v>-8.207108739636436</v>
+        <v>-9.670697378903727</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.5018552816145171</v>
       </c>
       <c r="E94">
-        <v>-29.75518683291533</v>
+        <v>-29.10327801731362</v>
       </c>
       <c r="F94">
-        <v>4.487838475592748</v>
+        <v>6.194600045381628</v>
       </c>
       <c r="G94">
-        <v>-8.174146783801335</v>
+        <v>-9.222077471345184</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.07469991668525815</v>
       </c>
       <c r="E95">
-        <v>-32.38263706655293</v>
+        <v>-30.52071505073038</v>
       </c>
       <c r="F95">
-        <v>3.857137759184067</v>
+        <v>5.71287623616202</v>
       </c>
       <c r="G95">
-        <v>-7.409638529068745</v>
+        <v>-9.09209502501513</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3503244302745502</v>
       </c>
       <c r="E96">
-        <v>-33.81987661156648</v>
+        <v>-33.02433105890123</v>
       </c>
       <c r="F96">
-        <v>3.511862628553593</v>
+        <v>5.476703719419464</v>
       </c>
       <c r="G96">
-        <v>-7.756716136500527</v>
+        <v>-8.917643766064645</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.7700132087034564</v>
       </c>
       <c r="E97">
-        <v>-36.29289798851298</v>
+        <v>-35.65069107456607</v>
       </c>
       <c r="F97">
-        <v>4.304698039977417</v>
+        <v>5.182114733431487</v>
       </c>
       <c r="G97">
-        <v>-7.672682794974069</v>
+        <v>-8.505464631508863</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.177583223313576</v>
       </c>
       <c r="E98">
-        <v>-39.60665808715585</v>
+        <v>-38.25876034755636</v>
       </c>
       <c r="F98">
-        <v>4.120911477787902</v>
+        <v>5.421706750812799</v>
       </c>
       <c r="G98">
-        <v>-7.637643991816737</v>
+        <v>-8.501459749306095</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.568105188676812</v>
       </c>
       <c r="E99">
-        <v>-42.17091305727487</v>
+        <v>-40.93072677677914</v>
       </c>
       <c r="F99">
-        <v>3.500427844925349</v>
+        <v>4.84231842480313</v>
       </c>
       <c r="G99">
-        <v>-7.993213046031116</v>
+        <v>-8.258926798280852</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.940292621078103</v>
       </c>
       <c r="E100">
-        <v>-43.38276405350695</v>
+        <v>-42.90349384965005</v>
       </c>
       <c r="F100">
-        <v>3.54317657311422</v>
+        <v>5.101498017791039</v>
       </c>
       <c r="G100">
-        <v>-6.640536669228091</v>
+        <v>-7.916902287005169</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.282846349227321</v>
       </c>
       <c r="E101">
-        <v>-45.72193885078538</v>
+        <v>-45.53271438961486</v>
       </c>
       <c r="F101">
-        <v>3.172291635858798</v>
+        <v>4.579248818491674</v>
       </c>
       <c r="G101">
-        <v>-7.459636898733155</v>
+        <v>-8.084351528962289</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.60783121354954</v>
       </c>
       <c r="E102">
-        <v>-48.80123874881053</v>
+        <v>-48.04664905132226</v>
       </c>
       <c r="F102">
-        <v>3.102581205443608</v>
+        <v>3.963859645156338</v>
       </c>
       <c r="G102">
-        <v>-7.560583949093142</v>
+        <v>-7.722212535984374</v>
       </c>
     </row>
   </sheetData>
